--- a/data/marcas.xlsx
+++ b/data/marcas.xlsx
@@ -1,43 +1,247 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luciano\Desktop\Distribuidora DAMAR\2026\app catalogo\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20460" windowHeight="6990"/>
+  </bookViews>
   <sheets>
     <sheet name="Marcas" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Marca</t>
+  </si>
+  <si>
+    <t>CALIPSO</t>
+  </si>
+  <si>
+    <t>NOSOTRAS</t>
+  </si>
+  <si>
+    <t>919</t>
+  </si>
+  <si>
+    <t>ISSUE</t>
+  </si>
+  <si>
+    <t>LEAU</t>
+  </si>
+  <si>
+    <t>ALGABO</t>
+  </si>
+  <si>
+    <t>PRIME</t>
+  </si>
+  <si>
+    <t>MAXX</t>
+  </si>
+  <si>
+    <t>SUIZA</t>
+  </si>
+  <si>
+    <t>FELPITA</t>
+  </si>
+  <si>
+    <t>FLORIPEL</t>
+  </si>
+  <si>
+    <t>DUFFY</t>
+  </si>
+  <si>
+    <t>DOREE</t>
+  </si>
+  <si>
+    <t>ANALIA</t>
+  </si>
+  <si>
+    <t>ARGENTINO</t>
+  </si>
+  <si>
+    <t>AROMAT</t>
+  </si>
+  <si>
+    <t>BRILL</t>
+  </si>
+  <si>
+    <t>BROSS</t>
+  </si>
+  <si>
+    <t>CANDELA</t>
+  </si>
+  <si>
+    <t>CARDON</t>
+  </si>
+  <si>
+    <t>CHANITA</t>
+  </si>
+  <si>
+    <t>CIEL</t>
+  </si>
+  <si>
+    <t>CLINSY</t>
+  </si>
+  <si>
+    <t>CLIPPER</t>
+  </si>
+  <si>
+    <t>COLBERT</t>
+  </si>
+  <si>
+    <t>COQUETERIA</t>
+  </si>
+  <si>
+    <t>CUPIDO</t>
+  </si>
+  <si>
+    <t>DANUBIO</t>
+  </si>
+  <si>
+    <t>DEPILORM</t>
+  </si>
+  <si>
+    <t>DESAFIO</t>
+  </si>
+  <si>
+    <t>DUKE</t>
+  </si>
+  <si>
+    <t>EL</t>
+  </si>
+  <si>
+    <t>ESCUDO</t>
+  </si>
+  <si>
+    <t>FLOWER</t>
+  </si>
+  <si>
+    <t>GAMUZA</t>
+  </si>
+  <si>
+    <t>GIGANTE</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>IDEAL</t>
+  </si>
+  <si>
+    <t>J&amp;J</t>
+  </si>
+  <si>
+    <t>KENIA</t>
+  </si>
+  <si>
+    <t>KEVIN</t>
+  </si>
+  <si>
+    <t>LAS</t>
+  </si>
+  <si>
+    <t>LISS</t>
+  </si>
+  <si>
+    <t>MAC</t>
+  </si>
+  <si>
+    <t>MUJERCITAS</t>
+  </si>
+  <si>
+    <t>MULTIMAX</t>
+  </si>
+  <si>
+    <t>PACO</t>
+  </si>
+  <si>
+    <t>PALOMA</t>
+  </si>
+  <si>
+    <t>PATITO</t>
+  </si>
+  <si>
+    <t>PAULA</t>
+  </si>
+  <si>
+    <t>PIBES</t>
+  </si>
+  <si>
+    <t>PINO</t>
+  </si>
+  <si>
+    <t>PRO</t>
+  </si>
+  <si>
+    <t>PURIFIC</t>
+  </si>
+  <si>
+    <t>Q-SOFT</t>
+  </si>
+  <si>
+    <t>ROBY</t>
+  </si>
+  <si>
+    <t>SAPHIRUS</t>
+  </si>
+  <si>
+    <t>SENS</t>
+  </si>
+  <si>
+    <t>SMELL</t>
+  </si>
+  <si>
+    <t>TENA</t>
+  </si>
+  <si>
+    <t>TENAPANTS</t>
+  </si>
+  <si>
+    <t>VAIS</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>VERITA</t>
+  </si>
+  <si>
+    <t>VERITAS</t>
+  </si>
+  <si>
+    <t>VILEDA</t>
+  </si>
+  <si>
+    <t>VILLENEUVE</t>
+  </si>
+  <si>
+    <t>VN</t>
+  </si>
+  <si>
+    <t>XMART</t>
+  </si>
+  <si>
+    <t>ESFREBOM</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="3">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="164" formatCode="&quot;$ &quot;#,##0.00;\-&quot;$ &quot;#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="0\ &quot;art.&quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -74,6 +278,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -398,588 +610,587 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B72"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>ID</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Marca</v>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="str">
-        <v>CALIPSO</v>
-      </c>
-    </row>
-    <row r="3">
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="str">
-        <v>NOSOTRAS</v>
-      </c>
-    </row>
-    <row r="4">
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="str">
-        <v>919</v>
-      </c>
-    </row>
-    <row r="5">
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="str">
-        <v>ISSUE</v>
-      </c>
-    </row>
-    <row r="6">
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="str">
-        <v>LEAU</v>
-      </c>
-    </row>
-    <row r="7">
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="str">
-        <v>ALGABO</v>
-      </c>
-    </row>
-    <row r="8">
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="str">
-        <v>ASANA</v>
-      </c>
-    </row>
-    <row r="9">
+      <c r="B8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" t="str">
-        <v>GO</v>
-      </c>
-    </row>
-    <row r="10">
+    </row>
+    <row r="10" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" t="str">
-        <v>PRIME</v>
-      </c>
-    </row>
-    <row r="11">
+      <c r="B10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" t="str">
-        <v>MAXX</v>
-      </c>
-    </row>
-    <row r="12">
+      <c r="B11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" t="str">
-        <v>SUIZA</v>
-      </c>
-    </row>
-    <row r="13">
+      <c r="B12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" t="str">
-        <v>FELPITA</v>
-      </c>
-    </row>
-    <row r="14">
+      <c r="B13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" t="str">
-        <v>FLORIPEL</v>
-      </c>
-    </row>
-    <row r="15">
+      <c r="B14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" t="str">
-        <v>DUFFY</v>
-      </c>
-    </row>
-    <row r="16">
+      <c r="B15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" t="str">
-        <v>DOREE</v>
-      </c>
-    </row>
-    <row r="17">
+      <c r="B16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" t="str">
-        <v>ANALIA</v>
-      </c>
-    </row>
-    <row r="18">
+      <c r="B17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" t="str">
-        <v>ARGENTINO</v>
-      </c>
-    </row>
-    <row r="19">
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" t="str">
-        <v>AROMAT</v>
-      </c>
-    </row>
-    <row r="20">
+      <c r="B19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" t="str">
-        <v>BRILL</v>
-      </c>
-    </row>
-    <row r="21">
+      <c r="B20" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" t="str">
-        <v>BROSS</v>
-      </c>
-    </row>
-    <row r="22">
+      <c r="B21" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" t="str">
-        <v>CANDELA</v>
-      </c>
-    </row>
-    <row r="23">
+      <c r="B22" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" t="str">
-        <v>CARDON</v>
-      </c>
-    </row>
-    <row r="24">
+      <c r="B23" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" t="str">
-        <v>CHANITA</v>
-      </c>
-    </row>
-    <row r="25">
+      <c r="B24" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" t="str">
-        <v>CIEL</v>
-      </c>
-    </row>
-    <row r="26">
+      <c r="B25" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" t="str">
-        <v>CLINSY</v>
-      </c>
-    </row>
-    <row r="27">
+      <c r="B26" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" t="str">
-        <v>CLIPPER</v>
-      </c>
-    </row>
-    <row r="28">
+      <c r="B27" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" t="str">
-        <v>COLBERT</v>
-      </c>
-    </row>
-    <row r="29">
+      <c r="B28" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" t="str">
-        <v>COQUETERIA</v>
-      </c>
-    </row>
-    <row r="30">
+      <c r="B29" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" t="str">
-        <v>CUPIDO</v>
-      </c>
-    </row>
-    <row r="31">
+      <c r="B30" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" t="str">
-        <v>DANUBIO</v>
-      </c>
-    </row>
-    <row r="32">
+      <c r="B31" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32" t="str">
-        <v>DEPILORM</v>
-      </c>
-    </row>
-    <row r="33">
+      <c r="B32" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33" t="str">
-        <v>DESAFIO</v>
-      </c>
-    </row>
-    <row r="34">
+      <c r="B33" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34" t="str">
-        <v>DUKE</v>
-      </c>
-    </row>
-    <row r="35">
+      <c r="B34" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
-      <c r="B35" t="str">
-        <v>EL</v>
-      </c>
-    </row>
-    <row r="36">
+      <c r="B35" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
-      <c r="B36" t="str">
-        <v>ESCUDO</v>
-      </c>
-    </row>
-    <row r="37">
+      <c r="B36" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
-      <c r="B37" t="str">
-        <v>FLOWER</v>
-      </c>
-    </row>
-    <row r="38">
+      <c r="B37" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
-      <c r="B38" t="str">
-        <v>GAMUZA</v>
-      </c>
-    </row>
-    <row r="39">
+      <c r="B38" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
-      <c r="B39" t="str">
-        <v>GIGANTE</v>
-      </c>
-    </row>
-    <row r="40">
+      <c r="B39" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
-      <c r="B40" t="str">
-        <v>I</v>
-      </c>
-    </row>
-    <row r="41">
+      <c r="B40" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
-      <c r="B41" t="str">
-        <v>IDEAL</v>
-      </c>
-    </row>
-    <row r="42">
+      <c r="B41" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
-      <c r="B42" t="str">
-        <v>J&amp;J</v>
-      </c>
-    </row>
-    <row r="43">
+      <c r="B42" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
-      <c r="B43" t="str">
-        <v>KENIA</v>
-      </c>
-    </row>
-    <row r="44">
+      <c r="B43" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
-      <c r="B44" t="str">
-        <v>KEVIN</v>
-      </c>
-    </row>
-    <row r="45">
+      <c r="B44" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
-      <c r="B45" t="str">
-        <v>LAS</v>
-      </c>
-    </row>
-    <row r="46">
+      <c r="B45" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
-      <c r="B46" t="str">
-        <v>LISS</v>
-      </c>
-    </row>
-    <row r="47">
+      <c r="B46" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
-      <c r="B47" t="str">
-        <v>MAC</v>
-      </c>
-    </row>
-    <row r="48">
+      <c r="B47" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
-      <c r="B48" t="str">
-        <v>MUJERCITAS</v>
-      </c>
-    </row>
-    <row r="49">
+      <c r="B48" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
-      <c r="B49" t="str">
-        <v>MULTIMAX</v>
-      </c>
-    </row>
-    <row r="50">
+      <c r="B49" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
-      <c r="B50" t="str">
-        <v>PACO</v>
-      </c>
-    </row>
-    <row r="51">
+      <c r="B50" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
-      <c r="B51" t="str">
-        <v>PALOMA</v>
-      </c>
-    </row>
-    <row r="52">
+      <c r="B51" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
-      <c r="B52" t="str">
-        <v>PATITO</v>
-      </c>
-    </row>
-    <row r="53">
+      <c r="B52" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
-      <c r="B53" t="str">
-        <v>PAULA</v>
-      </c>
-    </row>
-    <row r="54">
+      <c r="B53" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
-      <c r="B54" t="str">
-        <v>PIBES</v>
-      </c>
-    </row>
-    <row r="55">
+      <c r="B54" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
-      <c r="B55" t="str">
-        <v>PINO</v>
-      </c>
-    </row>
-    <row r="56">
+      <c r="B55" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
-      <c r="B56" t="str">
-        <v>PRO</v>
-      </c>
-    </row>
-    <row r="57">
+      <c r="B56" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
-      <c r="B57" t="str">
-        <v>PURIFIC</v>
-      </c>
-    </row>
-    <row r="58">
+      <c r="B57" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
-      <c r="B58" t="str">
-        <v>Q-SOFT</v>
-      </c>
-    </row>
-    <row r="59">
+      <c r="B58" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
-      <c r="B59" t="str">
-        <v>ROBY</v>
-      </c>
-    </row>
-    <row r="60">
+      <c r="B59" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
-      <c r="B60" t="str">
-        <v>SAPHIRUS</v>
-      </c>
-    </row>
-    <row r="61">
+      <c r="B60" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
-      <c r="B61" t="str">
-        <v>SENS</v>
-      </c>
-    </row>
-    <row r="62">
+      <c r="B61" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
-      <c r="B62" t="str">
-        <v>SMELL</v>
-      </c>
-    </row>
-    <row r="63">
+      <c r="B62" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
-      <c r="B63" t="str">
-        <v>TENA</v>
-      </c>
-    </row>
-    <row r="64">
+      <c r="B63" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
-      <c r="B64" t="str">
-        <v>TENAPANTS</v>
-      </c>
-    </row>
-    <row r="65">
+      <c r="B64" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>64</v>
       </c>
-      <c r="B65" t="str">
-        <v>VAIS</v>
-      </c>
-    </row>
-    <row r="66">
+      <c r="B65" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>65</v>
       </c>
-      <c r="B66" t="str">
-        <v>VALERIA</v>
-      </c>
-    </row>
-    <row r="67">
+      <c r="B66" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>66</v>
       </c>
-      <c r="B67" t="str">
-        <v>VERITA</v>
-      </c>
-    </row>
-    <row r="68">
+      <c r="B67" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>67</v>
       </c>
-      <c r="B68" t="str">
-        <v>VERITAS</v>
-      </c>
-    </row>
-    <row r="69">
+      <c r="B68" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>68</v>
       </c>
-      <c r="B69" t="str">
-        <v>VILEDA</v>
-      </c>
-    </row>
-    <row r="70">
+      <c r="B69" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>69</v>
       </c>
-      <c r="B70" t="str">
-        <v>VILLENEUVE</v>
-      </c>
-    </row>
-    <row r="71">
+      <c r="B70" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>70</v>
       </c>
-      <c r="B71" t="str">
-        <v>VN</v>
-      </c>
-    </row>
-    <row r="72">
+      <c r="B71" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>71</v>
       </c>
-      <c r="B72" t="str">
-        <v>XMART</v>
+      <c r="B72" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B72"/>
+    <ignoredError sqref="A1:B7 A10:B72 A8 A9" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/marcas.xlsx
+++ b/data/marcas.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
   <si>
     <t>ID</t>
   </si>
@@ -150,15 +150,9 @@
     <t>KEVIN</t>
   </si>
   <si>
-    <t>LAS</t>
-  </si>
-  <si>
     <t>LISS</t>
   </si>
   <si>
-    <t>MAC</t>
-  </si>
-  <si>
     <t>MUJERCITAS</t>
   </si>
   <si>
@@ -168,9 +162,6 @@
     <t>PACO</t>
   </si>
   <si>
-    <t>PALOMA</t>
-  </si>
-  <si>
     <t>PATITO</t>
   </si>
   <si>
@@ -198,43 +189,34 @@
     <t>SAPHIRUS</t>
   </si>
   <si>
-    <t>SENS</t>
-  </si>
-  <si>
-    <t>SMELL</t>
-  </si>
-  <si>
     <t>TENA</t>
   </si>
   <si>
-    <t>TENAPANTS</t>
-  </si>
-  <si>
-    <t>VAIS</t>
-  </si>
-  <si>
     <t>VALERIA</t>
   </si>
   <si>
-    <t>VERITA</t>
-  </si>
-  <si>
-    <t>VERITAS</t>
-  </si>
-  <si>
     <t>VILEDA</t>
   </si>
   <si>
     <t>VILLENEUVE</t>
   </si>
   <si>
-    <t>VN</t>
-  </si>
-  <si>
-    <t>XMART</t>
-  </si>
-  <si>
     <t>ESFREBOM</t>
+  </si>
+  <si>
+    <t>LAS PEPAS</t>
+  </si>
+  <si>
+    <t>MAC GREGOR</t>
+  </si>
+  <si>
+    <t>PALOMA HERRERA</t>
+  </si>
+  <si>
+    <t>SENS NATURAL</t>
+  </si>
+  <si>
+    <t>SMELL FRESH</t>
   </si>
 </sst>
 </file>
@@ -612,9 +594,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B72"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -622,7 +607,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -630,7 +615,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -638,7 +623,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -646,7 +631,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -654,7 +639,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -662,7 +647,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -670,20 +655,20 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -691,7 +676,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -699,7 +684,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -707,7 +692,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -715,7 +700,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -723,7 +708,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -731,7 +716,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -739,7 +724,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -747,7 +732,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -755,7 +740,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -763,7 +748,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -771,7 +756,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -779,7 +764,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -787,7 +772,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
@@ -795,7 +780,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
@@ -803,7 +788,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
@@ -811,7 +796,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
@@ -819,7 +804,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -827,7 +812,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>27</v>
       </c>
@@ -835,7 +820,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -843,7 +828,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -851,7 +836,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>30</v>
       </c>
@@ -859,7 +844,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -867,7 +852,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>32</v>
       </c>
@@ -875,7 +860,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>33</v>
       </c>
@@ -883,7 +868,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>34</v>
       </c>
@@ -891,7 +876,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>35</v>
       </c>
@@ -899,7 +884,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>36</v>
       </c>
@@ -907,7 +892,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>37</v>
       </c>
@@ -915,7 +900,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>38</v>
       </c>
@@ -923,7 +908,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>39</v>
       </c>
@@ -931,7 +916,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="41" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>40</v>
       </c>
@@ -939,7 +924,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="42" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>41</v>
       </c>
@@ -947,7 +932,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="43" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>42</v>
       </c>
@@ -955,7 +940,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="44" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>43</v>
       </c>
@@ -963,234 +948,216 @@
         <v>42</v>
       </c>
     </row>
-    <row r="45" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>63</v>
       </c>
-      <c r="B64" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>64</v>
       </c>
-      <c r="B65" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>66</v>
       </c>
-      <c r="B67" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>67</v>
       </c>
-      <c r="B68" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>70</v>
       </c>
-      <c r="B71" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>71</v>
-      </c>
-      <c r="B72" t="s">
-        <v>70</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:B7 A10:B72 A8 A9" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:B7 A10:B44 A8 A9 A46:B46 A45 A48:B50 A47 A52:B60 A51 A63:B63 A61 A62 A66:B66 A64 A65 A69:B70 A67 A68 A72 A71" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>